--- a/backtest_runs/20260410_193731/filter/BAHL/BAHL.xlsx
+++ b/backtest_runs/20260410_193731/filter/BAHL/BAHL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-1440.980000000005</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>98559.01999999999</v>
@@ -633,7 +633,7 @@
         <v>-1348.439999999995</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>99226.63</v>
@@ -679,7 +679,7 @@
         <v>-4461.75</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>94764.88</v>
@@ -817,7 +817,7 @@
         <v>-2465.530000000012</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>100502.36</v>
@@ -863,7 +863,7 @@
         <v>-3027.37999999999</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>97474.98000000001</v>
@@ -909,7 +909,7 @@
         <v>-2201.130000000008</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>95273.84999999999</v>
@@ -1047,7 +1047,7 @@
         <v>-456.0899999999985</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>96133.15000000001</v>
@@ -1093,7 +1093,7 @@
         <v>-112.3700000000105</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>96020.78</v>
@@ -1185,7 +1185,7 @@
         <v>-945.2300000000046</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>98830.03</v>
@@ -1231,7 +1231,7 @@
         <v>-1692.159999999983</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>97137.87000000001</v>
@@ -1277,7 +1277,7 @@
         <v>-1414.54000000001</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>95723.33</v>
@@ -1415,7 +1415,7 @@
         <v>-2842.299999999989</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>102452.31</v>
@@ -1507,7 +1507,7 @@
         <v>-251.179999999997</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>103529.74</v>
@@ -1645,7 +1645,7 @@
         <v>-4415.480000000004</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>110926.33</v>
